--- a/journal/journal_list-old.xlsx
+++ b/journal/journal_list-old.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\journal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CFFC13-1631-4BAA-BC03-1B4953E819A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFF162A-F165-40CB-8FD6-D4C0A9405156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="515">
   <si>
     <t>Category</t>
   </si>
@@ -515,9 +515,6 @@
     <t>International Journal of Tourism Research</t>
   </si>
   <si>
-    <t>https://onlinelibrary.wiley.com/toc/15221970/0/0</t>
-  </si>
-  <si>
     <t>Tourism Planning and Development</t>
   </si>
   <si>
@@ -627,9 +624,6 @@
   </si>
   <si>
     <t>https://link.springer.com/journal/42524/articles</t>
-  </si>
-  <si>
-    <t>Web|http://journal.hep.com.cn/fem/EN/article/showAsap.do</t>
   </si>
   <si>
     <t>Journal of Systems Science and Systems Engineering</t>
@@ -1572,10 +1566,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://journals.sagepub.com/action/doSearch?AllField=Journal+of+Marketing+Research&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Journal of Consumer Research</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1610,6 +1600,20 @@
   <si>
     <t>https://www.emerald.com/ijchm/earlycite</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web|http://journal.hep.com.cn/fem/EN/article/showAsap.do</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elsevier</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/15221970?af=R</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/action/doSearch?field1=AllField&amp;text1=&amp;publication%5B%5D=mrja&amp;publication=&amp;Ppub=&amp;access=&amp;startPage=0&amp;sortBy=FullEpubDateField</t>
   </si>
 </sst>
 </file>
@@ -2128,7 +2132,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>512</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -2139,8 +2143,9 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>10</v>
+      <c r="E2" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/applied-soft-computing/articles-in-press</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -2159,8 +2164,9 @@
       <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
+      <c r="E3" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/computers-and-industrial-engineering/articles-in-press</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -2179,8 +2185,9 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
+      <c r="E4" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/computers-and-operations-research/articles-in-press</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -2199,8 +2206,9 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
+      <c r="E5" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/decision-support-systems/articles-in-press</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -2219,8 +2227,9 @@
       <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
-        <v>10</v>
+      <c r="E6" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/european-journal-of-operational-research/articles-in-press</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -2239,8 +2248,9 @@
       <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="E7" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/expert-systems-with-applications/articles-in-press</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -2259,8 +2269,9 @@
       <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="E8" t="s">
-        <v>10</v>
+      <c r="E8" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/fuzzy-sets-and-systems/articles-in-press</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -2279,8 +2290,9 @@
       <c r="D9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
+      <c r="E9" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/information-fusion/articles-in-press</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -2299,8 +2311,9 @@
       <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
+      <c r="E10" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/information-sciences/articles-in-press</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -2319,8 +2332,9 @@
       <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="E11" t="s">
-        <v>10</v>
+      <c r="E11" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/international-journal-of-approximate-reasoning/articles-in-press</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -2339,8 +2353,9 @@
       <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" t="s">
-        <v>10</v>
+      <c r="E12" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/international-journal-of-production-economics/articles-in-press</v>
       </c>
       <c r="F12" t="s">
         <v>10</v>
@@ -2359,8 +2374,9 @@
       <c r="D13" t="s">
         <v>43</v>
       </c>
-      <c r="E13" t="s">
-        <v>10</v>
+      <c r="E13" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/knowledge-based-systems/articles-in-press</v>
       </c>
       <c r="F13" t="s">
         <v>10</v>
@@ -2379,8 +2395,9 @@
       <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="E14" t="s">
-        <v>10</v>
+      <c r="E14" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/omega/articles-in-press</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -2399,8 +2416,9 @@
       <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="E15" t="s">
-        <v>10</v>
+      <c r="E15" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/engineering-applications-of-artificial-intelligence/articles-in-press</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -2419,8 +2437,9 @@
       <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="E16" t="s">
-        <v>10</v>
+      <c r="E16" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/journal-of-management-science-and-engineering/articles-in-press</v>
       </c>
       <c r="F16" t="s">
         <v>10</v>
@@ -2439,8 +2458,9 @@
       <c r="D17" t="s">
         <v>55</v>
       </c>
-      <c r="E17" t="s">
-        <v>10</v>
+      <c r="E17" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/electronic-commerce-research-and-applications/articles-in-press</v>
       </c>
       <c r="F17" t="s">
         <v>10</v>
@@ -2459,8 +2479,9 @@
       <c r="D18" t="s">
         <v>58</v>
       </c>
-      <c r="E18" t="s">
-        <v>10</v>
+      <c r="E18" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/international-journal-of-forecasting/articles-in-press</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -2479,8 +2500,9 @@
       <c r="D19" t="s">
         <v>61</v>
       </c>
-      <c r="E19" t="s">
-        <v>10</v>
+      <c r="E19" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/information-and-management/articles-in-press</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -2499,8 +2521,9 @@
       <c r="D20" t="s">
         <v>64</v>
       </c>
-      <c r="E20" t="s">
-        <v>10</v>
+      <c r="E20" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/information-systems/articles-in-press</v>
       </c>
       <c r="F20" t="s">
         <v>10</v>
@@ -2519,8 +2542,9 @@
       <c r="D21" t="s">
         <v>67</v>
       </c>
-      <c r="E21" t="s">
-        <v>10</v>
+      <c r="E21" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/artificial-intelligence/articles-in-press</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -2539,8 +2563,9 @@
       <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="E22" t="s">
-        <v>10</v>
+      <c r="E22" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/pattern-recognition/articles-in-press</v>
       </c>
       <c r="F22" t="s">
         <v>10</v>
@@ -2559,8 +2584,9 @@
       <c r="D23" t="s">
         <v>73</v>
       </c>
-      <c r="E23" t="s">
-        <v>10</v>
+      <c r="E23" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/pattern-recognition-letters/articles-in-press</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -2579,8 +2605,9 @@
       <c r="D24" t="s">
         <v>76</v>
       </c>
-      <c r="E24" t="s">
-        <v>10</v>
+      <c r="E24" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/neurocomputing/articles-in-press</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -2599,8 +2626,9 @@
       <c r="D25" t="s">
         <v>79</v>
       </c>
-      <c r="E25" t="s">
-        <v>10</v>
+      <c r="E25" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/physica-a-statistical-mechanics-and-its-applications/articles-in-press</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -2619,8 +2647,9 @@
       <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="E26" t="s">
-        <v>10</v>
+      <c r="E26" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/reliability-engineering-and-system-safety/articles-in-press</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -2639,8 +2668,9 @@
       <c r="D27" t="s">
         <v>85</v>
       </c>
-      <c r="E27" t="s">
-        <v>10</v>
+      <c r="E27" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/journal-of-biomedical-informatics/articles-in-press</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -2659,8 +2689,9 @@
       <c r="D28" t="s">
         <v>88</v>
       </c>
-      <c r="E28" t="s">
-        <v>10</v>
+      <c r="E28" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/ai-open/articles-in-press</v>
       </c>
       <c r="F28" t="s">
         <v>10</v>
@@ -2679,8 +2710,9 @@
       <c r="D29" t="s">
         <v>91</v>
       </c>
-      <c r="E29" t="s">
-        <v>10</v>
+      <c r="E29" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/neural-networks/articles-in-press</v>
       </c>
       <c r="F29" t="s">
         <v>10</v>
@@ -2699,8 +2731,9 @@
       <c r="D30" t="s">
         <v>94</v>
       </c>
-      <c r="E30" t="s">
-        <v>10</v>
+      <c r="E30" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/advanced-engineering-informatics</v>
       </c>
       <c r="F30" t="s">
         <v>10</v>
@@ -2719,8 +2752,9 @@
       <c r="D31" t="s">
         <v>97</v>
       </c>
-      <c r="E31" t="s">
-        <v>10</v>
+      <c r="E31" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/computers-in-industry/articles-in-press</v>
       </c>
       <c r="F31" t="s">
         <v>10</v>
@@ -2739,8 +2773,9 @@
       <c r="D32" t="s">
         <v>100</v>
       </c>
-      <c r="E32" t="s">
-        <v>10</v>
+      <c r="E32" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/chaos-solitons-and-fractals/articles-in-press</v>
       </c>
       <c r="F32" t="s">
         <v>10</v>
@@ -2759,8 +2794,9 @@
       <c r="D33" t="s">
         <v>103</v>
       </c>
-      <c r="E33" t="s">
-        <v>10</v>
+      <c r="E33" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/safety-science/articles-in-press</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
@@ -2779,8 +2815,9 @@
       <c r="D34" t="s">
         <v>106</v>
       </c>
-      <c r="E34" t="s">
-        <v>10</v>
+      <c r="E34" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/technological-forecasting-and-social-change/articles-in-press</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
@@ -2799,8 +2836,9 @@
       <c r="D35" t="s">
         <v>109</v>
       </c>
-      <c r="E35" t="s">
-        <v>10</v>
+      <c r="E35" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/automation-in-construction</v>
       </c>
       <c r="F35" t="s">
         <v>10</v>
@@ -2819,8 +2857,9 @@
       <c r="D36" t="s">
         <v>112</v>
       </c>
-      <c r="E36" t="s">
-        <v>10</v>
+      <c r="E36" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/annual-reviews-in-control/articles-in-press</v>
       </c>
       <c r="F36" t="s">
         <v>10</v>
@@ -2839,8 +2878,9 @@
       <c r="D37" t="s">
         <v>115</v>
       </c>
-      <c r="E37" t="s">
-        <v>10</v>
+      <c r="E37" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/journal-of-cleaner-production/articles-in-press</v>
       </c>
       <c r="F37" t="s">
         <v>10</v>
@@ -2859,8 +2899,9 @@
       <c r="D38" t="s">
         <v>118</v>
       </c>
-      <c r="E38" t="s">
-        <v>10</v>
+      <c r="E38" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/energy/articles-in-press</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -2879,8 +2920,9 @@
       <c r="D39" t="s">
         <v>121</v>
       </c>
-      <c r="E39" t="s">
-        <v>10</v>
+      <c r="E39" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/journal-of-environmental-economics-and-management/articles-in-press</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -2899,8 +2941,9 @@
       <c r="D40" t="s">
         <v>124</v>
       </c>
-      <c r="E40" t="s">
-        <v>10</v>
+      <c r="E40" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/journal-of-retailing-and-consumer-services/articles-in-press</v>
       </c>
       <c r="F40" t="s">
         <v>10</v>
@@ -2919,8 +2962,9 @@
       <c r="D41" t="s">
         <v>127</v>
       </c>
-      <c r="E41" t="s">
-        <v>10</v>
+      <c r="E41" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/transportation-research-part-b-methodological/articles-in-press</v>
       </c>
       <c r="F41" t="s">
         <v>10</v>
@@ -2939,8 +2983,9 @@
       <c r="D42" t="s">
         <v>130</v>
       </c>
-      <c r="E42" t="s">
-        <v>10</v>
+      <c r="E42" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/transportation-research-part-d-transport-and-environment</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -2959,8 +3004,9 @@
       <c r="D43" t="s">
         <v>133</v>
       </c>
-      <c r="E43" t="s">
-        <v>10</v>
+      <c r="E43" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/transportation-research-part-e-logistics-and-transportation-review</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -2979,8 +3025,9 @@
       <c r="D44" t="s">
         <v>136</v>
       </c>
-      <c r="E44" t="s">
-        <v>10</v>
+      <c r="E44" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/euro-journal-on-decision-processes/articles-in-press</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -2999,8 +3046,9 @@
       <c r="D45" t="s">
         <v>139</v>
       </c>
-      <c r="E45" t="s">
-        <v>10</v>
+      <c r="E45" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/tourism-management/latest</v>
       </c>
       <c r="F45" t="s">
         <v>10</v>
@@ -3019,8 +3067,9 @@
       <c r="D46" t="s">
         <v>141</v>
       </c>
-      <c r="E46" t="s">
-        <v>10</v>
+      <c r="E46" t="str">
+        <f>"Web|"&amp;JournalListTable[[#This Row],[URL]]</f>
+        <v>Web|https://www.sciencedirect.com/journal/annals-of-tourism-research/articles-in-press</v>
       </c>
       <c r="F46" t="s">
         <v>10</v>
@@ -3137,7 +3186,7 @@
         <v>152</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -3217,7 +3266,7 @@
         <v>159</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>513</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -3234,10 +3283,10 @@
         <v>44</v>
       </c>
       <c r="C57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" t="s">
         <v>161</v>
-      </c>
-      <c r="D57" t="s">
-        <v>162</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -3254,10 +3303,10 @@
         <v>47</v>
       </c>
       <c r="C58" t="s">
+        <v>162</v>
+      </c>
+      <c r="D58" t="s">
         <v>163</v>
-      </c>
-      <c r="D58" t="s">
-        <v>164</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
@@ -3274,10 +3323,10 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" t="s">
         <v>165</v>
-      </c>
-      <c r="D59" t="s">
-        <v>166</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -3294,10 +3343,10 @@
         <v>53</v>
       </c>
       <c r="C60" t="s">
+        <v>166</v>
+      </c>
+      <c r="D60" t="s">
         <v>167</v>
-      </c>
-      <c r="D60" t="s">
-        <v>168</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -3308,16 +3357,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B61" t="s">
         <v>7</v>
       </c>
       <c r="C61" t="s">
+        <v>169</v>
+      </c>
+      <c r="D61" t="s">
         <v>170</v>
-      </c>
-      <c r="D61" t="s">
-        <v>171</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -3328,16 +3377,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" t="s">
         <v>172</v>
-      </c>
-      <c r="D62" t="s">
-        <v>173</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -3348,16 +3397,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
       </c>
       <c r="C63" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" t="s">
         <v>174</v>
-      </c>
-      <c r="D63" t="s">
-        <v>175</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -3368,16 +3417,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" t="s">
         <v>176</v>
-      </c>
-      <c r="D64" t="s">
-        <v>177</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -3388,16 +3437,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
       </c>
       <c r="C65" t="s">
+        <v>177</v>
+      </c>
+      <c r="D65" t="s">
         <v>178</v>
-      </c>
-      <c r="D65" t="s">
-        <v>179</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -3408,16 +3457,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
       </c>
       <c r="C66" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" t="s">
         <v>180</v>
-      </c>
-      <c r="D66" t="s">
-        <v>181</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -3428,16 +3477,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
+        <v>181</v>
+      </c>
+      <c r="D67" t="s">
         <v>182</v>
-      </c>
-      <c r="D67" t="s">
-        <v>183</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -3448,16 +3497,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B68" t="s">
         <v>29</v>
       </c>
       <c r="C68" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" t="s">
         <v>184</v>
-      </c>
-      <c r="D68" t="s">
-        <v>185</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -3468,16 +3517,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B69" t="s">
         <v>32</v>
       </c>
       <c r="C69" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" t="s">
         <v>186</v>
-      </c>
-      <c r="D69" t="s">
-        <v>187</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -3488,16 +3537,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B70" t="s">
         <v>35</v>
       </c>
       <c r="C70" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" t="s">
         <v>188</v>
-      </c>
-      <c r="D70" t="s">
-        <v>189</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -3508,16 +3557,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B71" t="s">
         <v>38</v>
       </c>
       <c r="C71" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" t="s">
         <v>190</v>
-      </c>
-      <c r="D71" t="s">
-        <v>191</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
@@ -3528,16 +3577,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B72" t="s">
         <v>41</v>
       </c>
       <c r="C72" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" t="s">
         <v>192</v>
-      </c>
-      <c r="D72" t="s">
-        <v>193</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -3548,16 +3597,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B73" t="s">
         <v>44</v>
       </c>
       <c r="C73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D73" t="s">
         <v>194</v>
-      </c>
-      <c r="D73" t="s">
-        <v>195</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
@@ -3568,19 +3617,19 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B74" t="s">
         <v>47</v>
       </c>
       <c r="C74" t="s">
+        <v>195</v>
+      </c>
+      <c r="D74" t="s">
         <v>196</v>
       </c>
-      <c r="D74" t="s">
-        <v>197</v>
-      </c>
       <c r="E74" t="s">
-        <v>198</v>
+        <v>511</v>
       </c>
       <c r="F74" t="s">
         <v>10</v>
@@ -3588,16 +3637,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B75" t="s">
         <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D75" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -3608,19 +3657,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B76" t="s">
         <v>53</v>
       </c>
       <c r="C76" t="s">
+        <v>199</v>
+      </c>
+      <c r="D76" t="s">
+        <v>200</v>
+      </c>
+      <c r="E76" t="s">
         <v>201</v>
-      </c>
-      <c r="D76" t="s">
-        <v>202</v>
-      </c>
-      <c r="E76" t="s">
-        <v>203</v>
       </c>
       <c r="F76" t="s">
         <v>10</v>
@@ -3628,16 +3677,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
         <v>56</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D77" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -3648,16 +3697,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
         <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D78" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -3668,16 +3717,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B79" t="s">
         <v>62</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D79" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -3688,16 +3737,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>65</v>
       </c>
       <c r="C80" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D80" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -3708,16 +3757,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
         <v>68</v>
       </c>
       <c r="C81" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -3728,16 +3777,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s">
         <v>71</v>
       </c>
       <c r="C82" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -3748,16 +3797,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
         <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D83" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -3768,16 +3817,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
         <v>77</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D84" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -3788,16 +3837,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
         <v>80</v>
       </c>
       <c r="C85" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D85" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -3808,16 +3857,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B86" t="s">
         <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D86" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -3828,16 +3877,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
         <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D87" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -3848,16 +3897,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
         <v>89</v>
       </c>
       <c r="C88" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -3868,16 +3917,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
         <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D89" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -3888,16 +3937,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
         <v>92</v>
       </c>
       <c r="C90" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D90" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -3908,16 +3957,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B91" t="s">
         <v>98</v>
       </c>
       <c r="C91" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D91" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -3928,16 +3977,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B92" t="s">
         <v>101</v>
       </c>
       <c r="C92" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D92" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -3948,16 +3997,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B93" t="s">
         <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D93" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -3968,16 +4017,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B94" t="s">
         <v>107</v>
       </c>
       <c r="C94" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D94" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -3988,16 +4037,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B95" t="s">
         <v>110</v>
       </c>
       <c r="C95" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D95" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -4008,16 +4057,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B96" t="s">
         <v>113</v>
       </c>
       <c r="C96" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D96" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
@@ -4028,16 +4077,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B97" t="s">
         <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
@@ -4048,16 +4097,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D98" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
@@ -4068,16 +4117,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B99" t="s">
         <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D99" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
@@ -4088,16 +4137,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D100" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
@@ -4108,16 +4157,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B101" t="s">
         <v>20</v>
       </c>
       <c r="C101" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D101" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
@@ -4128,16 +4177,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B102" t="s">
         <v>23</v>
       </c>
       <c r="C102" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D102" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
@@ -4148,16 +4197,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D103" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -4168,16 +4217,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B104" t="s">
         <v>29</v>
       </c>
       <c r="C104" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D104" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -4188,16 +4237,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B105" t="s">
         <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D105" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -4208,16 +4257,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B106" t="s">
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -4228,16 +4277,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B107" t="s">
         <v>38</v>
       </c>
       <c r="C107" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D107" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -4248,16 +4297,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B108" t="s">
         <v>41</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
@@ -4268,16 +4317,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s">
         <v>44</v>
       </c>
       <c r="C109" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
@@ -4288,19 +4337,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B110" t="s">
         <v>47</v>
       </c>
       <c r="C110" t="s">
+        <v>269</v>
+      </c>
+      <c r="D110" t="s">
+        <v>270</v>
+      </c>
+      <c r="E110" t="s">
         <v>271</v>
-      </c>
-      <c r="D110" t="s">
-        <v>272</v>
-      </c>
-      <c r="E110" t="s">
-        <v>273</v>
       </c>
       <c r="F110" t="s">
         <v>10</v>
@@ -4308,16 +4357,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B111" s="2">
         <v>15</v>
       </c>
       <c r="C111" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D111" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E111" t="s">
         <v>10</v>
@@ -4328,16 +4377,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B112" s="2">
         <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D112" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E112" t="s">
         <v>10</v>
@@ -4348,16 +4397,16 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B113" t="s">
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
@@ -4368,16 +4417,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B114" t="s">
         <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -4388,16 +4437,16 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B115" t="s">
         <v>62</v>
       </c>
       <c r="C115" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D115" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -4408,16 +4457,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B116" t="s">
         <v>65</v>
       </c>
       <c r="C116" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D116" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -4428,16 +4477,16 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B117" t="s">
         <v>68</v>
       </c>
       <c r="C117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D117" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -4448,19 +4497,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B118" s="3">
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E118" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F118" t="s">
         <v>10</v>
@@ -4468,19 +4517,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D119" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E119" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F119" t="s">
         <v>10</v>
@@ -4488,19 +4537,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B120" s="3">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D120" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E120" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F120" t="s">
         <v>10</v>
@@ -4508,19 +4557,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B121" s="3">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E121" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F121" t="s">
         <v>10</v>
@@ -4528,19 +4577,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B122" s="3">
         <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D122" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E122" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F122" t="s">
         <v>10</v>
@@ -4548,19 +4597,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B123" s="3">
         <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D123" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E123" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F123" t="s">
         <v>10</v>
@@ -4568,19 +4617,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B124" s="3">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D124" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E124" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F124" t="s">
         <v>10</v>
@@ -4588,19 +4637,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B125" s="3">
         <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E125" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F125" t="s">
         <v>10</v>
@@ -4608,132 +4657,132 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B126" s="3">
         <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E126" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B127" s="3">
         <v>10</v>
       </c>
       <c r="C127" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="E127" t="s">
         <v>489</v>
-      </c>
-      <c r="E127" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B128" s="3">
         <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E128" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B129" s="3">
         <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E129" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B130" s="3">
         <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E130" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B131" s="3">
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B132" s="3">
         <v>15</v>
       </c>
       <c r="C132" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>500</v>
-      </c>
       <c r="E132" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B133" s="3">
         <v>1</v>
       </c>
       <c r="C133" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D133" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -4744,16 +4793,16 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B134" s="3">
         <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D134" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -4764,16 +4813,16 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B135" s="3">
         <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D135" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -4784,16 +4833,16 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B136" s="3">
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D136" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -4804,16 +4853,16 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B137" s="3">
         <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D137" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -4824,16 +4873,16 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B138" s="3">
         <v>6</v>
       </c>
       <c r="C138" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D138" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -4844,16 +4893,16 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B139" s="3">
         <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D139" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -4864,16 +4913,16 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B140" s="3">
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D140" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -4884,16 +4933,16 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B141" s="3">
         <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D141" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -4904,16 +4953,16 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B142" s="3">
         <v>10</v>
       </c>
       <c r="C142" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D142" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -4924,16 +4973,16 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B143" s="3">
         <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D143" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
@@ -4944,16 +4993,16 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B144" s="4">
         <v>1</v>
       </c>
       <c r="C144" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
@@ -4964,16 +5013,16 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B145" s="4">
         <v>2</v>
       </c>
       <c r="C145" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D145" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
@@ -4984,16 +5033,16 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B146" s="4">
         <v>3</v>
       </c>
       <c r="C146" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D146" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
@@ -5004,16 +5053,16 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B147" s="4">
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D147" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -5024,16 +5073,16 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B148" s="4">
         <v>5</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D148" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -5044,16 +5093,16 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B149" s="4">
         <v>6</v>
       </c>
       <c r="C149" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D149" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -5064,16 +5113,16 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B150" s="4">
         <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D150" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -5084,16 +5133,16 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B151" s="4">
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D151" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -5104,16 +5153,16 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B152" s="4">
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D152" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -5124,16 +5173,16 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B153" s="4">
         <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D153" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
@@ -5144,16 +5193,16 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B154" s="4">
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D154" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
@@ -5164,16 +5213,16 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B155" s="4">
         <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D155" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
@@ -5184,16 +5233,16 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B156" s="4">
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D156" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -5204,16 +5253,16 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B157" s="4">
         <v>15</v>
       </c>
       <c r="C157" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D157" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
@@ -5224,16 +5273,16 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B158" s="4">
         <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D158" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
@@ -5244,16 +5293,16 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B159" s="4">
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D159" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
@@ -5264,16 +5313,16 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B160" s="4">
         <v>18</v>
       </c>
       <c r="C160" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D160" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
@@ -5284,16 +5333,16 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B161" s="4">
         <v>19</v>
       </c>
       <c r="C161" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D161" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
@@ -5304,30 +5353,30 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B162" s="2">
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B163" s="2">
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D163" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -5338,16 +5387,16 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B164" s="2">
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D164" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
@@ -5358,16 +5407,16 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B165" s="2">
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D165" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
@@ -5378,16 +5427,16 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B166" s="2">
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D166" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -5398,16 +5447,16 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B167" s="2">
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D167" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -5418,16 +5467,16 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B168" s="2">
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D168" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
@@ -5438,16 +5487,16 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B169" s="2">
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D169" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -5458,16 +5507,16 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B170" s="2">
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D170" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
@@ -5478,16 +5527,16 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B171" s="2">
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D171" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
@@ -5498,16 +5547,16 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B172" s="2">
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D172" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -5518,16 +5567,16 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B173" s="2">
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D173" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
@@ -5538,16 +5587,16 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B174" s="2">
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D174" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
@@ -5558,16 +5607,16 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B175" s="2">
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D175" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E175" t="s">
         <v>10</v>
@@ -5578,16 +5627,16 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B176" s="4">
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D176" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
@@ -5598,19 +5647,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
       </c>
       <c r="C177" t="s">
+        <v>392</v>
+      </c>
+      <c r="D177" t="s">
+        <v>393</v>
+      </c>
+      <c r="E177" t="s">
         <v>394</v>
-      </c>
-      <c r="D177" t="s">
-        <v>395</v>
-      </c>
-      <c r="E177" t="s">
-        <v>396</v>
       </c>
       <c r="F177" t="s">
         <v>10</v>
@@ -5618,19 +5667,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B178" t="s">
         <v>11</v>
       </c>
       <c r="C178" t="s">
+        <v>395</v>
+      </c>
+      <c r="D178" t="s">
+        <v>396</v>
+      </c>
+      <c r="E178" t="s">
         <v>397</v>
-      </c>
-      <c r="D178" t="s">
-        <v>398</v>
-      </c>
-      <c r="E178" t="s">
-        <v>399</v>
       </c>
       <c r="F178" t="s">
         <v>10</v>
@@ -5638,19 +5687,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B179" t="s">
         <v>14</v>
       </c>
       <c r="C179" t="s">
+        <v>398</v>
+      </c>
+      <c r="D179" t="s">
+        <v>399</v>
+      </c>
+      <c r="E179" t="s">
         <v>400</v>
-      </c>
-      <c r="D179" t="s">
-        <v>401</v>
-      </c>
-      <c r="E179" t="s">
-        <v>402</v>
       </c>
       <c r="F179" t="s">
         <v>10</v>
@@ -5658,19 +5707,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B180" t="s">
         <v>17</v>
       </c>
       <c r="C180" t="s">
+        <v>401</v>
+      </c>
+      <c r="D180" t="s">
+        <v>402</v>
+      </c>
+      <c r="E180" t="s">
         <v>403</v>
-      </c>
-      <c r="D180" t="s">
-        <v>404</v>
-      </c>
-      <c r="E180" t="s">
-        <v>405</v>
       </c>
       <c r="F180" t="s">
         <v>10</v>
@@ -5678,19 +5727,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B181" t="s">
         <v>20</v>
       </c>
       <c r="C181" t="s">
+        <v>404</v>
+      </c>
+      <c r="D181" t="s">
+        <v>405</v>
+      </c>
+      <c r="E181" t="s">
         <v>406</v>
-      </c>
-      <c r="D181" t="s">
-        <v>407</v>
-      </c>
-      <c r="E181" t="s">
-        <v>408</v>
       </c>
       <c r="F181" t="s">
         <v>10</v>
@@ -5698,19 +5747,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
       </c>
       <c r="C182" t="s">
+        <v>407</v>
+      </c>
+      <c r="D182" t="s">
+        <v>408</v>
+      </c>
+      <c r="E182" t="s">
         <v>409</v>
-      </c>
-      <c r="D182" t="s">
-        <v>410</v>
-      </c>
-      <c r="E182" t="s">
-        <v>411</v>
       </c>
       <c r="F182" t="s">
         <v>10</v>
@@ -5718,19 +5767,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B183" t="s">
         <v>26</v>
       </c>
       <c r="C183" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E183" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F183" t="s">
         <v>10</v>
@@ -5738,19 +5787,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B184" t="s">
         <v>29</v>
       </c>
       <c r="C184" t="s">
+        <v>412</v>
+      </c>
+      <c r="D184" t="s">
+        <v>413</v>
+      </c>
+      <c r="E184" t="s">
         <v>414</v>
-      </c>
-      <c r="D184" t="s">
-        <v>415</v>
-      </c>
-      <c r="E184" t="s">
-        <v>416</v>
       </c>
       <c r="F184" t="s">
         <v>10</v>
@@ -5758,19 +5807,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B185" t="s">
         <v>32</v>
       </c>
       <c r="C185" t="s">
+        <v>415</v>
+      </c>
+      <c r="D185" t="s">
+        <v>416</v>
+      </c>
+      <c r="E185" t="s">
         <v>417</v>
-      </c>
-      <c r="D185" t="s">
-        <v>418</v>
-      </c>
-      <c r="E185" t="s">
-        <v>419</v>
       </c>
       <c r="F185" t="s">
         <v>10</v>
@@ -5778,19 +5827,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B186" s="2">
         <v>10</v>
       </c>
       <c r="C186" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D186" t="s">
+        <v>419</v>
+      </c>
+      <c r="E186" t="s">
         <v>420</v>
-      </c>
-      <c r="D186" t="s">
-        <v>421</v>
-      </c>
-      <c r="E186" t="s">
-        <v>422</v>
       </c>
       <c r="F186" t="s">
         <v>10</v>
@@ -5798,19 +5847,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B187" s="2">
         <v>11</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D187" t="s">
+        <v>422</v>
+      </c>
+      <c r="E187" t="s">
         <v>423</v>
-      </c>
-      <c r="D187" t="s">
-        <v>424</v>
-      </c>
-      <c r="E187" t="s">
-        <v>425</v>
       </c>
       <c r="F187" t="s">
         <v>10</v>
@@ -5818,19 +5867,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B188" s="2">
         <v>12</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D188" t="s">
+        <v>425</v>
+      </c>
+      <c r="E188" t="s">
         <v>426</v>
-      </c>
-      <c r="D188" t="s">
-        <v>427</v>
-      </c>
-      <c r="E188" t="s">
-        <v>428</v>
       </c>
       <c r="F188" t="s">
         <v>10</v>
@@ -5838,19 +5887,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B189" s="2">
         <v>13</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D189" t="s">
+        <v>428</v>
+      </c>
+      <c r="E189" t="s">
         <v>429</v>
-      </c>
-      <c r="D189" t="s">
-        <v>430</v>
-      </c>
-      <c r="E189" t="s">
-        <v>431</v>
       </c>
       <c r="F189" t="s">
         <v>10</v>
@@ -5858,19 +5907,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B190" t="s">
         <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E190" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F190" t="s">
         <v>10</v>
@@ -5878,19 +5927,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B191" t="s">
         <v>50</v>
       </c>
       <c r="C191" t="s">
+        <v>432</v>
+      </c>
+      <c r="D191" t="s">
+        <v>433</v>
+      </c>
+      <c r="E191" t="s">
         <v>434</v>
-      </c>
-      <c r="D191" t="s">
-        <v>435</v>
-      </c>
-      <c r="E191" t="s">
-        <v>436</v>
       </c>
       <c r="F191" t="s">
         <v>10</v>
@@ -5898,19 +5947,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B192" t="s">
         <v>53</v>
       </c>
       <c r="C192" t="s">
+        <v>435</v>
+      </c>
+      <c r="D192" t="s">
+        <v>436</v>
+      </c>
+      <c r="E192" t="s">
         <v>437</v>
-      </c>
-      <c r="D192" t="s">
-        <v>438</v>
-      </c>
-      <c r="E192" t="s">
-        <v>439</v>
       </c>
       <c r="F192" t="s">
         <v>10</v>
@@ -5918,19 +5967,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B193" t="s">
         <v>56</v>
       </c>
       <c r="C193" t="s">
+        <v>438</v>
+      </c>
+      <c r="D193" t="s">
+        <v>439</v>
+      </c>
+      <c r="E193" t="s">
         <v>440</v>
-      </c>
-      <c r="D193" t="s">
-        <v>441</v>
-      </c>
-      <c r="E193" t="s">
-        <v>442</v>
       </c>
       <c r="F193" t="s">
         <v>10</v>
@@ -5938,19 +5987,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B194" t="s">
         <v>59</v>
       </c>
       <c r="C194" t="s">
+        <v>441</v>
+      </c>
+      <c r="D194" t="s">
+        <v>442</v>
+      </c>
+      <c r="E194" t="s">
         <v>443</v>
-      </c>
-      <c r="D194" t="s">
-        <v>444</v>
-      </c>
-      <c r="E194" t="s">
-        <v>445</v>
       </c>
       <c r="F194" t="s">
         <v>10</v>
@@ -5958,19 +6007,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B195" t="s">
         <v>62</v>
       </c>
       <c r="C195" t="s">
+        <v>444</v>
+      </c>
+      <c r="D195" t="s">
+        <v>445</v>
+      </c>
+      <c r="E195" t="s">
         <v>446</v>
-      </c>
-      <c r="D195" t="s">
-        <v>447</v>
-      </c>
-      <c r="E195" t="s">
-        <v>448</v>
       </c>
       <c r="F195" t="s">
         <v>10</v>
@@ -5978,19 +6027,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B196" t="s">
         <v>65</v>
       </c>
       <c r="C196" t="s">
+        <v>447</v>
+      </c>
+      <c r="D196" t="s">
+        <v>448</v>
+      </c>
+      <c r="E196" t="s">
         <v>449</v>
-      </c>
-      <c r="D196" t="s">
-        <v>450</v>
-      </c>
-      <c r="E196" t="s">
-        <v>451</v>
       </c>
       <c r="F196" t="s">
         <v>10</v>
@@ -5998,19 +6047,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B197" t="s">
         <v>68</v>
       </c>
       <c r="C197" t="s">
+        <v>450</v>
+      </c>
+      <c r="D197" t="s">
+        <v>451</v>
+      </c>
+      <c r="E197" t="s">
         <v>452</v>
-      </c>
-      <c r="D197" t="s">
-        <v>453</v>
-      </c>
-      <c r="E197" t="s">
-        <v>454</v>
       </c>
       <c r="F197" t="s">
         <v>10</v>
@@ -6018,19 +6067,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B198" t="s">
         <v>71</v>
       </c>
       <c r="C198" t="s">
+        <v>453</v>
+      </c>
+      <c r="D198" t="s">
+        <v>454</v>
+      </c>
+      <c r="E198" t="s">
         <v>455</v>
-      </c>
-      <c r="D198" t="s">
-        <v>456</v>
-      </c>
-      <c r="E198" t="s">
-        <v>457</v>
       </c>
       <c r="F198" t="s">
         <v>10</v>
@@ -6038,19 +6087,19 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B199" t="s">
         <v>74</v>
       </c>
       <c r="C199" t="s">
+        <v>456</v>
+      </c>
+      <c r="D199" t="s">
+        <v>457</v>
+      </c>
+      <c r="E199" t="s">
         <v>458</v>
-      </c>
-      <c r="D199" t="s">
-        <v>459</v>
-      </c>
-      <c r="E199" t="s">
-        <v>460</v>
       </c>
       <c r="F199" t="s">
         <v>10</v>
@@ -6058,19 +6107,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B200" t="s">
         <v>77</v>
       </c>
       <c r="C200" t="s">
+        <v>459</v>
+      </c>
+      <c r="D200" t="s">
+        <v>460</v>
+      </c>
+      <c r="E200" t="s">
         <v>461</v>
-      </c>
-      <c r="D200" t="s">
-        <v>462</v>
-      </c>
-      <c r="E200" t="s">
-        <v>463</v>
       </c>
       <c r="F200" t="s">
         <v>10</v>
@@ -6078,19 +6127,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B201" t="s">
         <v>80</v>
       </c>
       <c r="C201" t="s">
+        <v>462</v>
+      </c>
+      <c r="D201" t="s">
+        <v>463</v>
+      </c>
+      <c r="E201" t="s">
         <v>464</v>
-      </c>
-      <c r="D201" t="s">
-        <v>465</v>
-      </c>
-      <c r="E201" t="s">
-        <v>466</v>
       </c>
       <c r="F201" t="s">
         <v>10</v>
@@ -6098,19 +6147,19 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B202" t="s">
         <v>83</v>
       </c>
       <c r="C202" t="s">
+        <v>465</v>
+      </c>
+      <c r="D202" t="s">
+        <v>466</v>
+      </c>
+      <c r="E202" t="s">
         <v>467</v>
-      </c>
-      <c r="D202" t="s">
-        <v>468</v>
-      </c>
-      <c r="E202" t="s">
-        <v>469</v>
       </c>
       <c r="F202" t="s">
         <v>10</v>
@@ -6118,19 +6167,19 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B203" t="s">
         <v>86</v>
       </c>
       <c r="C203" t="s">
+        <v>468</v>
+      </c>
+      <c r="D203" t="s">
+        <v>469</v>
+      </c>
+      <c r="E203" t="s">
         <v>470</v>
-      </c>
-      <c r="D203" t="s">
-        <v>471</v>
-      </c>
-      <c r="E203" t="s">
-        <v>472</v>
       </c>
       <c r="F203" t="s">
         <v>10</v>
@@ -6138,19 +6187,19 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B204" t="s">
         <v>89</v>
       </c>
       <c r="C204" t="s">
+        <v>471</v>
+      </c>
+      <c r="D204" t="s">
+        <v>472</v>
+      </c>
+      <c r="E204" t="s">
         <v>473</v>
-      </c>
-      <c r="D204" t="s">
-        <v>474</v>
-      </c>
-      <c r="E204" t="s">
-        <v>475</v>
       </c>
       <c r="F204" t="s">
         <v>10</v>
@@ -6158,19 +6207,19 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B205" t="s">
         <v>92</v>
       </c>
       <c r="C205" t="s">
+        <v>474</v>
+      </c>
+      <c r="D205" t="s">
+        <v>475</v>
+      </c>
+      <c r="E205" t="s">
         <v>476</v>
-      </c>
-      <c r="D205" t="s">
-        <v>477</v>
-      </c>
-      <c r="E205" t="s">
-        <v>478</v>
       </c>
       <c r="F205" t="s">
         <v>10</v>
@@ -6182,8 +6231,9 @@
     <hyperlink ref="D52" r:id="rId1" xr:uid="{05653E1F-7B16-4257-AB0C-7800B47E2144}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>